--- a/system_analysis_overview.xlsx
+++ b/system_analysis_overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>CIF #</t>
   </si>
@@ -28,31 +28,34 @@
     <t>In-In</t>
   </si>
   <si>
+    <t>451623</t>
+  </si>
+  <si>
     <t>1300872</t>
   </si>
   <si>
-    <t>451623</t>
-  </si>
-  <si>
     <t>1538436</t>
   </si>
   <si>
+    <t>457677</t>
+  </si>
+  <si>
+    <t>451606</t>
+  </si>
+  <si>
     <t>1410412</t>
   </si>
   <si>
-    <t>451606</t>
-  </si>
-  <si>
     <t>450249</t>
   </si>
   <si>
-    <t>457677</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Unique Total</t>
+    <t>No duplicates total</t>
+  </si>
+  <si>
+    <t>Fraction</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -553,6 +556,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/system_analysis_overview.xlsx
+++ b/system_analysis_overview.xlsx
@@ -28,25 +28,25 @@
     <t>In-In</t>
   </si>
   <si>
+    <t>450249</t>
+  </si>
+  <si>
+    <t>457677</t>
+  </si>
+  <si>
+    <t>1538436</t>
+  </si>
+  <si>
     <t>451623</t>
   </si>
   <si>
+    <t>451606</t>
+  </si>
+  <si>
+    <t>1410412</t>
+  </si>
+  <si>
     <t>1300872</t>
-  </si>
-  <si>
-    <t>1538436</t>
-  </si>
-  <si>
-    <t>457677</t>
-  </si>
-  <si>
-    <t>451606</t>
-  </si>
-  <si>
-    <t>1410412</t>
-  </si>
-  <si>
-    <t>450249</t>
   </si>
   <si>
     <t>Total</t>

--- a/system_analysis_overview.xlsx
+++ b/system_analysis_overview.xlsx
@@ -28,25 +28,25 @@
     <t>In-In</t>
   </si>
   <si>
+    <t>1410412</t>
+  </si>
+  <si>
+    <t>451606</t>
+  </si>
+  <si>
     <t>450249</t>
   </si>
   <si>
+    <t>1300872</t>
+  </si>
+  <si>
+    <t>1538436</t>
+  </si>
+  <si>
+    <t>451623</t>
+  </si>
+  <si>
     <t>457677</t>
-  </si>
-  <si>
-    <t>1538436</t>
-  </si>
-  <si>
-    <t>451623</t>
-  </si>
-  <si>
-    <t>451606</t>
-  </si>
-  <si>
-    <t>1410412</t>
-  </si>
-  <si>
-    <t>1300872</t>
   </si>
   <si>
     <t>Total</t>

--- a/system_analysis_overview.xlsx
+++ b/system_analysis_overview.xlsx
@@ -28,25 +28,25 @@
     <t>In-In</t>
   </si>
   <si>
+    <t>1300872</t>
+  </si>
+  <si>
     <t>1410412</t>
   </si>
   <si>
+    <t>457677</t>
+  </si>
+  <si>
+    <t>451623</t>
+  </si>
+  <si>
+    <t>450249</t>
+  </si>
+  <si>
+    <t>1538436</t>
+  </si>
+  <si>
     <t>451606</t>
-  </si>
-  <si>
-    <t>450249</t>
-  </si>
-  <si>
-    <t>1300872</t>
-  </si>
-  <si>
-    <t>1538436</t>
-  </si>
-  <si>
-    <t>451623</t>
-  </si>
-  <si>
-    <t>457677</t>
   </si>
   <si>
     <t>Total</t>

--- a/system_analysis_overview.xlsx
+++ b/system_analysis_overview.xlsx
@@ -28,16 +28,16 @@
     <t>In-In</t>
   </si>
   <si>
+    <t>457677</t>
+  </si>
+  <si>
+    <t>451623</t>
+  </si>
+  <si>
     <t>1300872</t>
   </si>
   <si>
     <t>1410412</t>
-  </si>
-  <si>
-    <t>457677</t>
-  </si>
-  <si>
-    <t>451623</t>
   </si>
   <si>
     <t>450249</t>

--- a/system_analysis_overview.xlsx
+++ b/system_analysis_overview.xlsx
@@ -28,25 +28,25 @@
     <t>In-In</t>
   </si>
   <si>
+    <t>451606</t>
+  </si>
+  <si>
+    <t>1410412</t>
+  </si>
+  <si>
+    <t>451623</t>
+  </si>
+  <si>
+    <t>1300872</t>
+  </si>
+  <si>
+    <t>450249</t>
+  </si>
+  <si>
+    <t>1538436</t>
+  </si>
+  <si>
     <t>457677</t>
-  </si>
-  <si>
-    <t>451623</t>
-  </si>
-  <si>
-    <t>1300872</t>
-  </si>
-  <si>
-    <t>1410412</t>
-  </si>
-  <si>
-    <t>450249</t>
-  </si>
-  <si>
-    <t>1538436</t>
-  </si>
-  <si>
-    <t>451606</t>
   </si>
   <si>
     <t>Total</t>

--- a/system_analysis_overview.xlsx
+++ b/system_analysis_overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>CIF #</t>
   </si>
@@ -25,28 +25,64 @@
     <t>Co-In</t>
   </si>
   <si>
+    <t>Er-Co</t>
+  </si>
+  <si>
+    <t>Er-Er</t>
+  </si>
+  <si>
+    <t>Er-In</t>
+  </si>
+  <si>
     <t>In-In</t>
   </si>
   <si>
-    <t>451606</t>
-  </si>
-  <si>
-    <t>1410412</t>
-  </si>
-  <si>
-    <t>451623</t>
-  </si>
-  <si>
-    <t>1300872</t>
-  </si>
-  <si>
-    <t>450249</t>
-  </si>
-  <si>
-    <t>1538436</t>
-  </si>
-  <si>
-    <t>457677</t>
+    <t>1229705</t>
+  </si>
+  <si>
+    <t>1803318</t>
+  </si>
+  <si>
+    <t>1234749</t>
+  </si>
+  <si>
+    <t>1234747</t>
+  </si>
+  <si>
+    <t>1803512</t>
+  </si>
+  <si>
+    <t>1000761</t>
+  </si>
+  <si>
+    <t>1634753</t>
+  </si>
+  <si>
+    <t>1956508</t>
+  </si>
+  <si>
+    <t>1233938</t>
+  </si>
+  <si>
+    <t>1818414</t>
+  </si>
+  <si>
+    <t>1814810</t>
+  </si>
+  <si>
+    <t>1710931</t>
+  </si>
+  <si>
+    <t>1840445</t>
+  </si>
+  <si>
+    <t>1920543</t>
+  </si>
+  <si>
+    <t>1140826</t>
+  </si>
+  <si>
+    <t>1925389</t>
   </si>
   <si>
     <t>Total</t>
@@ -413,10 +449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -429,145 +465,451 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="C18">
+        <v>26</v>
+      </c>
+      <c r="D18">
+        <v>37</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>22</v>
+      </c>
+      <c r="G18">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>0.05825242718446602</v>
+      </c>
+      <c r="C20">
+        <v>0.2524271844660194</v>
+      </c>
+      <c r="D20">
+        <v>0.3592233009708738</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0.2135922330097087</v>
+      </c>
+      <c r="G20">
+        <v>0.116504854368932</v>
       </c>
     </row>
   </sheetData>
